--- a/reports/tables/comparativa_random_forest_diabetes.xlsx
+++ b/reports/tables/comparativa_random_forest_diabetes.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,11 @@
     <font>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="00856404"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +60,11 @@
         <fgColor rgb="0028A745"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBA8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,11 +78,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -558,76 +567,76 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Balanced Random Forest Optimizado</t>
+          <t>Random Forest (Class Weight)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5884</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0.8903</v>
+        <v>0.892</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.1721</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.1097</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.1758</v>
+        <v>0.8279</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.367</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.2936</v>
+        <v>0.2343</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.7958</v>
+        <v>0.7944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Random Forest (Class Weight)</t>
+          <t>Random Forest (SMOTE)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.892</v>
+        <v>0.8912</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.1721</v>
+        <v>0.1372</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.8279</v>
+        <v>0.1615</v>
       </c>
       <c r="E6" t="n">
-        <v>0.367</v>
+        <v>0.3374</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.2343</v>
+        <v>0.195</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.7944</v>
+        <v>0.7937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Random Forest (SMOTE)</t>
+          <t>Balanced Random Forest Optimizado</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8912</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0.1372</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.1615</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.3374</v>
+        <v>0.5163</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.9352</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.0611</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.1584</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.195</v>
+        <v>0.2709</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.7937</v>
+        <v>0.7922</v>
       </c>
     </row>
     <row r="8">
